--- a/data/1/6.3 fig1 b 18.xlsx
+++ b/data/1/6.3 fig1 b 18.xlsx
@@ -1341,7 +1341,7 @@
         <v>6.06</v>
       </c>
       <c r="I3">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="J3">
         <v>4.82</v>
@@ -1444,7 +1444,7 @@
         <v>5.88</v>
       </c>
       <c r="J5">
-        <v>6.26</v>
+        <v>6</v>
       </c>
       <c r="K5">
         <v>5.54</v>
@@ -1491,13 +1491,13 @@
         <v>7.68</v>
       </c>
       <c r="I6">
-        <v>4.73</v>
+        <v>5.73</v>
       </c>
       <c r="J6">
-        <v>4.81</v>
+        <v>5.81</v>
       </c>
       <c r="K6">
-        <v>4.78</v>
+        <v>5.78</v>
       </c>
       <c r="L6">
         <v>6.45</v>
@@ -1644,7 +1644,7 @@
         <v>4.88</v>
       </c>
       <c r="K10">
-        <v>5.29</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>5.68</v>
@@ -2103,13 +2103,13 @@
         <v>6.76</v>
       </c>
       <c r="O20">
-        <v>9.39</v>
+        <v>8.39</v>
       </c>
       <c r="P20">
-        <v>9.37</v>
+        <v>8.37</v>
       </c>
       <c r="Q20">
-        <v>8.96</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -2232,10 +2232,10 @@
         <v>6.08</v>
       </c>
       <c r="I24">
-        <v>5.77</v>
+        <v>4.77</v>
       </c>
       <c r="J24">
-        <v>5.51</v>
+        <v>4.51</v>
       </c>
       <c r="K24">
         <v>5.03</v>
@@ -2285,7 +2285,7 @@
         <v>5.63</v>
       </c>
       <c r="J25">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="K25">
         <v>5.65</v>
@@ -2332,22 +2332,22 @@
         <v>8.1</v>
       </c>
       <c r="I26">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="J26">
-        <v>5.58</v>
+        <v>5.98</v>
       </c>
       <c r="K26">
-        <v>5.28</v>
+        <v>5.88</v>
       </c>
       <c r="L26">
-        <v>7.15</v>
+        <v>6.75</v>
       </c>
       <c r="M26">
-        <v>7.28</v>
+        <v>6.68</v>
       </c>
       <c r="N26">
-        <v>7.41</v>
+        <v>6.71</v>
       </c>
       <c r="O26">
         <v>8.13</v>
@@ -2385,7 +2385,7 @@
         <v>6.31</v>
       </c>
       <c r="J27">
-        <v>6.34</v>
+        <v>6</v>
       </c>
       <c r="K27">
         <v>5.94</v>
